--- a/Documents/devfiles/DBdesignVer2.xlsx
+++ b/Documents/devfiles/DBdesignVer2.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\devfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADDA3CE-382A-4ACA-AFA4-07F89AFD74F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B6F22B-038E-4CB1-99A0-7A07052C3223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6408" yWindow="4272" windowWidth="21300" windowHeight="12168" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="3120" yWindow="3012" windowWidth="23040" windowHeight="12168" activeTab="1" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="ReferenceTable" sheetId="12" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="14" r:id="rId2"/>
+    <sheet name="UserInRoles" sheetId="13" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
   <si>
     <t>Companies</t>
   </si>
@@ -56,6 +64,9 @@
     <t>IsActive</t>
   </si>
   <si>
+    <t>CategoryName</t>
+  </si>
+  <si>
     <t>TypeName</t>
   </si>
   <si>
@@ -71,6 +82,9 @@
     <t>TypeId</t>
   </si>
   <si>
+    <t>DisplayOrder</t>
+  </si>
+  <si>
     <t>MatrixId</t>
   </si>
   <si>
@@ -138,13 +152,82 @@
   </si>
   <si>
     <t>CompensationItems</t>
+  </si>
+  <si>
+    <t>AspNetUsers</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>AspNetRoles</t>
+  </si>
+  <si>
+    <t>AspNetUserRoles</t>
+  </si>
+  <si>
+    <t>UserId</t>
+  </si>
+  <si>
+    <t>RoleId</t>
+  </si>
+  <si>
+    <t>CompenItemCategory</t>
+  </si>
+  <si>
+    <t>CategoryId</t>
+  </si>
+  <si>
+    <t>CmpnyCmpnstnName</t>
+  </si>
+  <si>
+    <t>JOCompanyCompensation</t>
+  </si>
+  <si>
+    <t>JobOfferId</t>
+  </si>
+  <si>
+    <t>OptionNumber</t>
+  </si>
+  <si>
+    <t>Escalate</t>
+  </si>
+  <si>
+    <t>Increase</t>
+  </si>
+  <si>
+    <t>BandStatus</t>
+  </si>
+  <si>
+    <t>JOCmpnyCompensationItems</t>
+  </si>
+  <si>
+    <t>JOCmpnyCmpnstnId</t>
+  </si>
+  <si>
+    <t>CurrentSalary</t>
+  </si>
+  <si>
+    <t>ProposedSalary</t>
+  </si>
+  <si>
+    <t>TotalMonthly</t>
+  </si>
+  <si>
+    <t>TotalAnnually</t>
+  </si>
+  <si>
+    <t>DiffTotalMonthly</t>
+  </si>
+  <si>
+    <t>DiffTotalAnnually</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +242,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -181,9 +277,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3E0DE8-4720-4CDB-8DB3-CDF187788EC3}">
-  <dimension ref="B2:H16"/>
+  <dimension ref="B2:H21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
@@ -529,142 +631,396 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="H5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" t="s">
         <v>24</v>
-      </c>
-      <c r="H9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H15" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="H16" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H21" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7AE70E-E5CC-4406-BB70-6FBBBFBDDCCE}">
+  <dimension ref="B2:D25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5710F30C-E88B-4A3C-8A63-0D8128BE2FFF}">
+  <dimension ref="B2:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Documents/devfiles/DBdesignVer2.xlsx
+++ b/Documents/devfiles/DBdesignVer2.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\devfiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\devfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B6F22B-038E-4CB1-99A0-7A07052C3223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E150BAF6-FC3A-4BAE-843F-5F387F4732E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3012" windowWidth="23040" windowHeight="12168" activeTab="1" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BEC21941-B947-480A-A7E6-7B63159DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="ReferenceTable" sheetId="12" r:id="rId1"/>
-    <sheet name="Analysis" sheetId="14" r:id="rId2"/>
-    <sheet name="UserInRoles" sheetId="13" r:id="rId3"/>
+    <sheet name="UserInRoles" sheetId="13" r:id="rId2"/>
+    <sheet name="Analysis" sheetId="14" r:id="rId3"/>
+    <sheet name="Letter" sheetId="15" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="64">
   <si>
     <t>Name</t>
   </si>
@@ -221,6 +222,18 @@
   </si>
   <si>
     <t>DiffTotalAnnually</t>
+  </si>
+  <si>
+    <t>MessageBody</t>
+  </si>
+  <si>
+    <t>JOItemLetter</t>
+  </si>
+  <si>
+    <t>JOWorkFlowStatus</t>
+  </si>
+  <si>
+    <t>FlowName</t>
   </si>
 </sst>
 </file>
@@ -620,16 +633,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3E0DE8-4720-4CDB-8DB3-CDF187788EC3}">
-  <dimension ref="B2:H21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:J21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.21875" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1796875" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -642,8 +656,11 @@
       <c r="H2" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J2" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -656,8 +673,11 @@
       <c r="H3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -670,13 +690,16 @@
       <c r="H4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
@@ -687,7 +710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -701,7 +724,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>26</v>
       </c>
@@ -712,7 +735,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>27</v>
       </c>
@@ -726,7 +749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D10" t="s">
         <v>5</v>
       </c>
@@ -737,7 +760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
         <v>19</v>
       </c>
@@ -748,7 +771,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="F12" t="s">
         <v>10</v>
       </c>
@@ -756,37 +779,37 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H15" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H17" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H21" s="2" t="s">
         <v>7</v>
       </c>
@@ -797,177 +820,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7AE70E-E5CC-4406-BB70-6FBBBFBDDCCE}">
-  <dimension ref="B2:D25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5710F30C-E88B-4A3C-8A63-0D8128BE2FFF}">
+  <dimension ref="B2:B11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D25" t="s">
-        <v>35</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -976,51 +873,319 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5710F30C-E88B-4A3C-8A63-0D8128BE2FFF}">
-  <dimension ref="B2:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7AE70E-E5CC-4406-BB70-6FBBBFBDDCCE}">
+  <dimension ref="B2:D25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B6" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D23" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2552A1-D2D6-4D6E-936E-AAD262657723}">
+  <dimension ref="B2:D26"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B8" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
